--- a/stories/arbres/TREE-AUT-019.xlsx
+++ b/stories/arbres/TREE-AUT-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara écoute maman. Sara entend les mots : une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-019.xlsx
+++ b/stories/arbres/TREE-AUT-019.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara écoute maman. Sara entend les mots : une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Sara a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Sara rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Sara rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Sara a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Sara rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Sara a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Sara rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Sara rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Sara a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Sara rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Sara a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Sara rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Sara rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Sara a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Sara rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Sara a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Sara rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Sara rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Sara a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Sara rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Sara a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Sara rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-019.xlsx
+++ b/stories/arbres/TREE-AUT-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enchaîner le matin — à la ferme</t>
+          <t>Le bidon de lait de Sarah</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le bidon de lait sonne le matin à la ferme. Sarah se lève, s'habille, va jouer un moment dehors, puis déjeune. Une étape après l'autre.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara écoute maman. Sara entend les mots : une étape après l'autre.</t>
+          <t>Le bidon de lait fait ding. Papa le pose près de l'évier. La cuisine de la ferme est sombre. Une petite lampe fait un rond jaune. Ça sent le lait chaud. Ça sent le pain du four. Le sol de pierre est froid. Les bottes de Sarah attendent. Elles sont près de la porte grise. Une poule picore déjà dehors. On entend ses petits pas secs. Sarah, le matin est là. Tu entends le bidon ? Oui, maman. Il fait ding. On se lève. C'est la première étape. En ce moment, Sarah est sous la couverture. La couverture a de petits moutons. Elle sent le savon de la lessive. Encore un peu. Le matin est là. On fait l'étape dite. Une étape après l'autre. Sarah pousse la couverture. Ses pieds touchent le tapis rêche. Le tapis est un peu froid. Bravo, Sarah. Tu es debout. Le pull rouge attend sur la chaise. Sarah met le pull. Elle met le pantalon gris. Elle met les chaussettes, une puis l'autre. Tu as fait l'étape de l'habillage. Bravo. J'ai fini, papa. Très bien. Maintenant, la prochaine étape. On va un peu dehors. Puis on déjeune. Une étape après l'autre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara écoute maman. Sara entend les mots : une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le bidon de lait fait ding.
+narrateur|Papa le pose près de l'évier.
+narrateur|La cuisine de la ferme est sombre.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Ça sent le lait chaud.
+narrateur|Ça sent le pain du four.
+narrateur|Le sol de pierre est froid.
+narrateur|Les bottes de Sarah attendent.
+narrateur|Elles sont près de la porte grise.
+narrateur|Une poule picore déjà dehors.
+narrateur|On entend ses petits pas secs.
+maman|Sarah, le matin est là.
+maman|Tu entends le bidon ?
+enfant-f|Oui, maman.
+enfant-f|Il fait ding.
+papa|On se lève.
+papa|C'est la première étape.
+narrateur|En ce moment, Sarah est sous la couverture.
+narrateur|La couverture a de petits moutons.
+narrateur|Elle sent le savon de la lessive.
+enfant-f|Encore un peu.
+maman|Le matin est là.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah pousse la couverture.
+narrateur|Ses pieds touchent le tapis rêche.
+narrateur|Le tapis est un peu froid.
+papa|Bravo, Sarah.
+papa|Tu es debout.
+narrateur|Le pull rouge attend sur la chaise.
+narrateur|Sarah met le pull.
+narrateur|Elle met le pantalon gris.
+narrateur|Elle met les chaussettes, une puis l'autre.
+maman|Tu as fait l'étape de l'habillage.
+maman|Bravo.
+enfant-f|J'ai fini, papa.
+papa|Très bien.
+papa|Maintenant, la prochaine étape.
+maman|On va un peu dehors.
+maman|Puis on déjeune.
+maman|Une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On va où, pour l'étape du dehors ? Le bac à sable. Le toboggan. Ou les balançoires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,10 +1568,12 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>maman|On va où, pour l'étape du dehors ?
+narrateur|Le bac à sable.
+narrateur|Le toboggan.
+narrateur|Ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1545,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers le bac à sable. Le sable est pâle, un peu frais. Il glisse entre les doigts. Ça fait chh, tout doux. Une poule passe près du bac. Elle picore un grain. C'est l'étape du dehors. On fait l'étape dite. Une étape après l'autre, Sarah. Sarah pose les genoux sur le sable. Le sable est un peu froid le matin. Il est frais, maman. Oui. Tu as fait l'étape. Bravo. Je suis là, tout près. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1738,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah va vers le bac à sable.
+narrateur|Le sable est pâle, un peu frais.
+narrateur|Il glisse entre les doigts.
+narrateur|Ça fait chh, tout doux.
+narrateur|Une poule passe près du bac.
+narrateur|Elle picore un grain.
+maman|C'est l'étape du dehors.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre, Sarah.
+narrateur|Sarah pose les genoux sur le sable.
+narrateur|Le sable est un peu froid le matin.
+enfant-f|Il est frais, maman.
+maman|Oui. Tu as fait l'étape.
+maman|Bravo.
+papa|Je suis là, tout près.
+papa|On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Sarah se prépare. On avance comment ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,10 +1936,10 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah se prépare.
+narrateur|On avance comment ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1898,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Sarah a fait l'étape dite. Bravo. Le sable reste sur ses doigts. J'ai fait l'étape. Oui. On continue.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,10 +2108,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Oui.
+maman|Une étape après l'autre.
+papa|Sarah a fait l'étape dite.
+papa|Bravo.
+narrateur|Le sable reste sur ses doigts.
+enfant-f|J'ai fait l'étape.
+maman|Oui. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2070,7 +2141,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Tu prends quel jeu, pour cette étape ? Le ballon. Le seau. Ou le doudou.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,10 +2305,12 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+          <t>papa|Tu prends quel jeu, pour cette étape ?
+narrateur|Le ballon.
+narrateur|Le seau.
+narrateur|Ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2262,7 +2335,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah a choisi le ballon. Le ballon est rouge, un peu rêche. Il fait toc contre le sol. Le sable du bac reste collé aux doigts. C'est l'étape du ballon. On fait l'étape dite. Une étape après l'autre. Sarah pose le ballon près de maman. Le ballon reste à sa place. Il est rouge. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2475,20 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le ballon.
+narrateur|Le ballon est rouge, un peu rêche.
+narrateur|Il fait toc contre le sol.
+narrateur|Le sable du bac reste collé aux doigts.
+maman|C'est l'étape du ballon.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le ballon près de maman.
+narrateur|Le ballon reste à sa place.
+enfant-f|Il est rouge.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2513,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,10 +2681,12 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2626,7 +2711,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Une plume jaune tombe près du pain. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. La plume reste sur la croûte.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,10 +2851,25 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Une plume jaune tombe près du pain.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|La plume reste sur la croûte.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2794,7 +2894,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le ballon. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. La plume reste sur la croûte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,10 +3034,19 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|La plume reste sur la croûte.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2962,7 +3071,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Une goutte de lait brille sur le bois. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Le ballon a un peu de sable.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,10 +3211,25 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Une goutte de lait brille sur le bois.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le ballon a un peu de sable.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3130,7 +3254,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le ballon. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le ballon a un peu de sable. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,10 +3394,19 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le ballon a un peu de sable.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3298,7 +3431,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Un œuf encore chaud attend dans l'assiette. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Le ballon roule jusqu'à la chaise.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,10 +3571,25 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Un œuf encore chaud attend dans l'assiette.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le ballon roule jusqu'à la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3466,7 +3614,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le ballon. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le ballon roule jusqu'à la chaise. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,10 +3754,19 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le ballon roule jusqu'à la chaise.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3634,7 +3791,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah a choisi le seau. Le seau est jaune, un peu froid. Il fait clic contre une pierre. Le sable du bac reste collé aux doigts. C'est l'étape du seau. On fait l'étape dite. Une étape après l'autre. Sarah pose le seau près de maman. Le seau reste à sa place. Il est jaune. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,10 +3931,20 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le seau.
+narrateur|Le seau est jaune, un peu froid.
+narrateur|Il fait clic contre une pierre.
+narrateur|Le sable du bac reste collé aux doigts.
+maman|C'est l'étape du seau.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le seau près de maman.
+narrateur|Le seau reste à sa place.
+enfant-f|Il est jaune.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3802,7 +3969,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3970,10 +4137,12 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3998,7 +4167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Du sable est collé au seau jaune. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Une miette reste sur le pain.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4138,10 +4307,25 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Du sable est collé au seau jaune.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Une miette reste sur le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4166,7 +4350,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le seau. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Une miette reste sur le pain. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4306,10 +4490,19 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Une miette reste sur le pain.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4334,7 +4527,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Le seau fait clic près du bol. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. La vapeur du lait monte tout droit.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4474,10 +4667,25 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Le seau fait clic près du bol.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|La vapeur du lait monte tout droit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4502,7 +4710,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le seau. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. La vapeur du lait monte tout droit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4642,10 +4850,19 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|La vapeur du lait monte tout droit.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4670,7 +4887,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Le seau jaune est près des œufs. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Un grain de sable brille sur la coquille.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4810,10 +5027,25 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Le seau jaune est près des œufs.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Un grain de sable brille sur la coquille.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4838,7 +5070,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le seau. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Un grain de sable brille sur la coquille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4978,10 +5210,19 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Un grain de sable brille sur la coquille.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5006,7 +5247,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+          <t>Sarah a choisi le doudou. Le doudou est gris, tout doux. Il sent le savon de la lessive. Le sable du bac reste collé aux doigts. C'est l'étape du doudou. On fait l'étape dite. Une étape après l'autre. Sarah pose le doudou près de maman. Le doudou reste à sa place. Il est doux. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5146,10 +5387,20 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le doudou.
+narrateur|Le doudou est gris, tout doux.
+narrateur|Il sent le savon de la lessive.
+narrateur|Le sable du bac reste collé aux doigts.
+maman|C'est l'étape du doudou.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le doudou près de maman.
+narrateur|Le doudou reste à sa place.
+enfant-f|Il est doux.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5174,7 +5425,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5342,10 +5593,12 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5370,7 +5623,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Le doudou a une miette sur l'oreille. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Le pain sent encore le four.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5510,10 +5763,25 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Le doudou a une miette sur l'oreille.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le pain sent encore le four.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5538,7 +5806,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le doudou. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le pain sent encore le four. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5678,10 +5946,19 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le pain sent encore le four.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5706,7 +5983,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Le doudou est sur les genoux de Sarah. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Le lait est tiède dans le bol bleu.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5846,10 +6123,25 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Le doudou est sur les genoux de Sarah.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le lait est tiède dans le bol bleu.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5874,7 +6166,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le doudou. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le lait est tiède dans le bol bleu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6014,10 +6306,19 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le lait est tiède dans le bol bleu.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6042,7 +6343,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Le doudou veille près des œufs. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. La poule chante une fois, dehors.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6182,10 +6483,25 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Le doudou veille près des œufs.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|La poule chante une fois, dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6210,7 +6526,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au bac à sable. Elle a pris le doudou. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. La poule chante une fois, dehors. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6350,10 +6666,19 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|La poule chante une fois, dehors.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6378,7 +6703,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers le toboggan. Le bois est tiède, déjà. Une paille est collée en bas. Ça sent le foin chaud. Le soleil touche la rampe. C'est l'étape du toboggan. On fait l'étape dite. Une étape après l'autre. Sarah monte la petite échelle. Les marches sont lisses. Elle glisse, tout doucement. C'est lisse, papa. Oui. Bravo, Sarah. Tu as fait l'étape dite. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6518,11 +6843,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Sarah va vers le toboggan.
+narrateur|Le bois est tiède, déjà.
+narrateur|Une paille est collée en bas.
+narrateur|Ça sent le foin chaud.
+narrateur|Le soleil touche la rampe.
+maman|C'est l'étape du toboggan.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah monte la petite échelle.
+narrateur|Les marches sont lisses.
+narrateur|Elle glisse, tout doucement.
+enfant-f|C'est lisse, papa.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape dite.
+maman|Je suis là.
+papa|On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6547,7 +6885,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Sarah se prépare. On avance comment ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6703,10 +7041,10 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>narrateur|Sarah se prépare.
+narrateur|On avance comment ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6731,7 +7069,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Sarah a fait l'étape dite. Bravo. Le bois du toboggan est encore tiède. J'ai fait l'étape. Oui. On continue.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6875,10 +7213,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Oui.
+maman|Une étape après l'autre.
+papa|Sarah a fait l'étape dite.
+papa|Bravo.
+narrateur|Le bois du toboggan est encore tiède.
+enfant-f|J'ai fait l'étape.
+maman|Oui. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6903,7 +7246,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Tu prends quel jeu, pour cette étape ? Le ballon. Le seau. Ou le doudou.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7067,10 +7410,12 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+          <t>papa|Tu prends quel jeu, pour cette étape ?
+narrateur|Le ballon.
+narrateur|Le seau.
+narrateur|Ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7095,7 +7440,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah a choisi le ballon. Le ballon est rouge, un peu rêche. Il fait toc contre le sol. Le bois du toboggan est encore tiède. C'est l'étape du ballon. On fait l'étape dite. Une étape après l'autre. Sarah pose le ballon près de maman. Le ballon reste à sa place. Il est rouge. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7235,10 +7580,20 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le ballon.
+narrateur|Le ballon est rouge, un peu rêche.
+narrateur|Il fait toc contre le sol.
+narrateur|Le bois du toboggan est encore tiède.
+maman|C'est l'étape du ballon.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le ballon près de maman.
+narrateur|Le ballon reste à sa place.
+enfant-f|Il est rouge.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,7 +7618,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7431,10 +7786,12 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7459,7 +7816,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Une paille est collée au pain. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Le toboggan est encore tiède.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7599,10 +7956,25 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Une paille est collée au pain.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le toboggan est encore tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7627,7 +7999,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le ballon. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le toboggan est encore tiède. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7767,10 +8139,19 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le toboggan est encore tiède.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7795,7 +8176,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Le bois du toboggan sent le soleil. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Le bol de lait fume un peu.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7935,10 +8316,25 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Le bois du toboggan sent le soleil.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le bol de lait fume un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7963,7 +8359,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le ballon. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le bol de lait fume un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8103,10 +8499,19 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le bol de lait fume un peu.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8131,7 +8536,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Une paille est collée au ballon. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Les œufs sont dans l'assiette ronde.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8271,10 +8676,25 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Une paille est collée au ballon.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Les œufs sont dans l'assiette ronde.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8299,7 +8719,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le ballon. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Les œufs sont dans l'assiette ronde. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8439,10 +8859,19 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Les œufs sont dans l'assiette ronde.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8467,7 +8896,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah a choisi le seau. Le seau est jaune, un peu froid. Il fait clic contre une pierre. Le bois du toboggan est encore tiède. C'est l'étape du seau. On fait l'étape dite. Une étape après l'autre. Sarah pose le seau près de maman. Le seau reste à sa place. Il est jaune. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8607,10 +9036,20 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le seau.
+narrateur|Le seau est jaune, un peu froid.
+narrateur|Il fait clic contre une pierre.
+narrateur|Le bois du toboggan est encore tiède.
+maman|C'est l'étape du seau.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le seau près de maman.
+narrateur|Le seau reste à sa place.
+enfant-f|Il est jaune.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8635,7 +9074,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8803,10 +9242,12 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8831,7 +9272,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Le seau a glissé près de la planche. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Le pain a une croûte dorée.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8971,10 +9412,25 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Le seau a glissé près de la planche.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le pain a une croûte dorée.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8999,7 +9455,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le seau. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le pain a une croûte dorée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9139,10 +9595,19 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le pain a une croûte dorée.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9167,7 +9632,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Une goutte d'eau tombe du seau. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Elle s'arrête près du bol.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9307,10 +9772,25 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Une goutte d'eau tombe du seau.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Elle s'arrête près du bol.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9335,7 +9815,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le seau. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Elle s'arrête près du bol. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9475,10 +9955,19 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Elle s'arrête près du bol.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9503,7 +9992,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Le seau fait tic contre la table. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Les œufs sont chauds, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9643,10 +10132,25 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Le seau fait tic contre la table.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Les œufs sont chauds, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9671,7 +10175,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le seau. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Les œufs sont chauds, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9811,10 +10315,19 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9839,7 +10352,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+          <t>Sarah a choisi le doudou. Le doudou est gris, tout doux. Il sent le savon de la lessive. Le bois du toboggan est encore tiède. C'est l'étape du doudou. On fait l'étape dite. Une étape après l'autre. Sarah pose le doudou près de maman. Le doudou reste à sa place. Il est doux. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9979,10 +10492,20 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le doudou.
+narrateur|Le doudou est gris, tout doux.
+narrateur|Il sent le savon de la lessive.
+narrateur|Le bois du toboggan est encore tiède.
+maman|C'est l'étape du doudou.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le doudou près de maman.
+narrateur|Le doudou reste à sa place.
+enfant-f|Il est doux.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10007,7 +10530,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10175,10 +10698,12 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10203,7 +10728,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Le doudou a glissé du toboggan. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Une miette reste sur sa patte.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10343,10 +10868,25 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Le doudou a glissé du toboggan.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Une miette reste sur sa patte.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10371,7 +10911,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le doudou. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Une miette reste sur sa patte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10511,10 +11051,19 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Une miette reste sur sa patte.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10539,7 +11088,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Le doudou est contre le bol bleu. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Le lait sent le matin.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10679,10 +11228,25 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Le doudou est contre le bol bleu.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le lait sent le matin.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10707,7 +11271,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le doudou. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le lait sent le matin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10847,10 +11411,19 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le lait sent le matin.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10875,7 +11448,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Le doudou est assis près des œufs. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Une paille brille sur la nappe.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11015,10 +11588,25 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Le doudou est assis près des œufs.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Une paille brille sur la nappe.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11043,7 +11631,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée au toboggan. Elle a pris le doudou. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Une paille brille sur la nappe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11183,10 +11771,19 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée au toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Une paille brille sur la nappe.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11211,7 +11808,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers les balançoires. La corde est rêche, un peu. Le siège de bois est frais. Un pommier fait de l'ombre. Une pomme verte brille. C'est l'étape des balançoires. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit sur le bois. La corde fait criiic. Ça chante, maman. Oui. La corde chante. Bravo. Tu as fait l'étape. Je suis là, tout près. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11351,11 +11948,23 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Sarah va vers les balançoires.
+narrateur|La corde est rêche, un peu.
+narrateur|Le siège de bois est frais.
+narrateur|Un pommier fait de l'ombre.
+narrateur|Une pomme verte brille.
+maman|C'est l'étape des balançoires.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah s'assoit sur le bois.
+narrateur|La corde fait criiic.
+enfant-f|Ça chante, maman.
+maman|Oui. La corde chante.
+maman|Bravo. Tu as fait l'étape.
+papa|Je suis là, tout près.
+papa|On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11380,7 +11989,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Sarah se prépare. On avance comment ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11536,10 +12145,10 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr"/>
+          <t>narrateur|Sarah se prépare.
+narrateur|On avance comment ?</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11564,7 +12173,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Sarah a fait l'étape dite. Bravo. La corde se tait une seconde. J'ai fait l'étape. Oui. On continue.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11708,10 +12317,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Sara respire. Sara retient : une étape après l'autre. On continue, avec maman.</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr"/>
+          <t>narrateur|Oui.
+maman|Une étape après l'autre.
+papa|Sarah a fait l'étape dite.
+papa|Bravo.
+narrateur|La corde se tait une seconde.
+enfant-f|J'ai fait l'étape.
+maman|Oui. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11736,7 +12350,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Tu prends quel jeu, pour cette étape ? Le ballon. Le seau. Ou le doudou.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11900,10 +12514,12 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr"/>
+          <t>papa|Tu prends quel jeu, pour cette étape ?
+narrateur|Le ballon.
+narrateur|Le seau.
+narrateur|Ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11928,7 +12544,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah a choisi le ballon. Le ballon est rouge, un peu rêche. Il fait toc contre le sol. La corde de la balançoire fait criiic. C'est l'étape du ballon. On fait l'étape dite. Une étape après l'autre. Sarah pose le ballon près de maman. Le ballon reste à sa place. Il est rouge. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12068,10 +12684,20 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le ballon.
+narrateur|Le ballon est rouge, un peu rêche.
+narrateur|Il fait toc contre le sol.
+narrateur|La corde de la balançoire fait criiic.
+maman|C'est l'étape du ballon.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le ballon près de maman.
+narrateur|Le ballon reste à sa place.
+enfant-f|Il est rouge.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12096,7 +12722,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,10 +12890,12 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12292,7 +12920,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. La corde de la balançoire craque encore. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Le pain est chaud sous les doigts.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12432,10 +13060,25 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|La corde de la balançoire craque encore.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le pain est chaud sous les doigts.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12460,7 +13103,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le ballon. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le pain est chaud sous les doigts. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12600,10 +13243,19 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le pain est chaud sous les doigts.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12628,7 +13280,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Une pomme verte est sur la table. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Elle est près du bol de lait.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12768,10 +13420,25 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Une pomme verte est sur la table.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Elle est près du bol de lait.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12796,7 +13463,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le ballon. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Elle est près du bol de lait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12936,10 +13603,19 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Elle est près du bol de lait.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12964,7 +13640,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. L'ombre de la balançoire est sur le sol. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le ballon dans le sac. Comme je t'ai dit. Sarah met le ballon dans le sac. Tu as mis ce que maman a dit. Bravo. Les œufs attendent, tout calmes.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13104,10 +13780,25 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|L'ombre de la balançoire est sur le sol.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le ballon dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le ballon dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Les œufs attendent, tout calmes.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13132,7 +13823,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le ballon. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Les œufs attendent, tout calmes. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13272,10 +13963,19 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Les œufs attendent, tout calmes.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13300,7 +14000,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah a choisi le seau. Le seau est jaune, un peu froid. Il fait clic contre une pierre. La corde de la balançoire fait criiic. C'est l'étape du seau. On fait l'étape dite. Une étape après l'autre. Sarah pose le seau près de maman. Le seau reste à sa place. Il est jaune. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13440,10 +14140,20 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le seau.
+narrateur|Le seau est jaune, un peu froid.
+narrateur|Il fait clic contre une pierre.
+narrateur|La corde de la balançoire fait criiic.
+maman|C'est l'étape du seau.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le seau près de maman.
+narrateur|Le seau reste à sa place.
+enfant-f|Il est jaune.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13468,7 +14178,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13636,10 +14346,12 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13664,7 +14376,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Le seau sent l'herbe mouillée. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Le pain craque un tout petit peu.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13804,10 +14516,25 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Le seau sent l'herbe mouillée.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le pain craque un tout petit peu.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13832,7 +14559,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le seau. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le pain craque un tout petit peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13972,10 +14699,19 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le pain craque un tout petit peu.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14000,7 +14736,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Une feuille est tombée dans le seau. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Le lait est blanc, tout tiède.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14140,10 +14876,25 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Une feuille est tombée dans le seau.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le lait est blanc, tout tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14168,7 +14919,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le seau. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le lait est blanc, tout tiède. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14308,10 +15059,19 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le lait est blanc, tout tiède.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14336,7 +15096,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Le seau est près du panier d'œufs. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le seau dans le sac. Comme je t'ai dit. Sarah met le seau dans le sac. Tu as mis ce que maman a dit. Bravo. Une feuille tourne près de la porte.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14476,10 +15236,25 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Le seau est près du panier d'œufs.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le seau dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le seau dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Une feuille tourne près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14504,7 +15279,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le seau. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Une feuille tourne près de la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14644,10 +15419,19 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Une feuille tourne près de la porte.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14672,7 +15456,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+          <t>Sarah a choisi le doudou. Le doudou est gris, tout doux. Il sent le savon de la lessive. La corde de la balançoire fait criiic. C'est l'étape du doudou. On fait l'étape dite. Une étape après l'autre. Sarah pose le doudou près de maman. Le doudou reste à sa place. Il est doux. Oui. Bravo, Sarah. Tu as fait l'étape.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14812,10 +15596,20 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Sara répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Sarah a choisi le doudou.
+narrateur|Le doudou est gris, tout doux.
+narrateur|Il sent le savon de la lessive.
+narrateur|La corde de la balançoire fait criiic.
+maman|C'est l'étape du doudou.
+maman|On fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Sarah pose le doudou près de maman.
+narrateur|Le doudou reste à sa place.
+enfant-f|Il est doux.
+papa|Oui. Bravo, Sarah.
+maman|Tu as fait l'étape.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14840,7 +15634,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Ensuite, quelle étape, pour déjeuner ? Le pain. Le lait. Ou les œufs.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15008,10 +15802,12 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr"/>
+          <t>maman|Ensuite, quelle étape, pour déjeuner ?
+narrateur|Le pain.
+narrateur|Le lait.
+narrateur|Ou les œufs.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15036,7 +15832,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du pain. Le pain est chaud, tout doré. Ça sent le four de la ferme. Le doudou a voyagé sur la balançoire. On fait l'étape dite. Une étape après l'autre. Sarah casse un bout de croûte. La croûte fait cric. C'est chaud, maman. Oui. Bravo, Sarah. Tu as fait l'étape du pain. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Une miette reste sur le pain.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15176,10 +15972,25 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du pain.
+narrateur|Le pain est chaud, tout doré.
+narrateur|Ça sent le four de la ferme.
+narrateur|Le doudou a voyagé sur la balançoire.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah casse un bout de croûte.
+narrateur|La croûte fait cric.
+enfant-f|C'est chaud, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du pain.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Une miette reste sur le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15204,7 +16015,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le doudou. Puis c'était l'étape du pain. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Une miette reste sur le pain. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15344,10 +16155,19 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape du pain.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Une miette reste sur le pain.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15372,7 +16192,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape du lait. Le bol bleu fume un peu. Ça sent le lait chaud. Le doudou est sur les genoux. On fait l'étape dite. Une étape après l'autre. Sarah s'assoit à sa petite table. Elle pose les pieds par terre. Il est tiède, papa. Oui. Bravo, Sarah. Tu as fait l'étape du lait. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Le bol de lait est bien plein.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15512,10 +16332,25 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|C'est l'étape du lait.
+narrateur|Le bol bleu fume un peu.
+narrateur|Ça sent le lait chaud.
+narrateur|Le doudou est sur les genoux.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah s'assoit à sa petite table.
+narrateur|Elle pose les pieds par terre.
+enfant-f|Il est tiède, papa.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape du lait.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Le bol de lait est bien plein.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15540,7 +16375,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le doudou. Puis c'était l'étape du lait. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Le bol de lait est bien plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15680,10 +16515,19 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape du lait.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Le bol de lait est bien plein.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15708,7 +16552,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
+          <t>C'est l'étape des œufs. Les œufs sont chauds, tout doux. Ils sont dans l'assiette ronde. Une feuille est sur le doudou. On fait l'étape dite. Une étape après l'autre. Sarah goûte un petit bout. Ça sent la ferme, le matin. C'est bon, maman. Oui. Bravo, Sarah. Tu as fait l'étape des œufs. Ensuite, on met le doudou dans le sac. Comme je t'ai dit. Sarah met le doudou dans le sac. Tu as mis ce que maman a dit. Bravo. Les œufs sont chauds dans l'assiette.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15848,10 +16692,25 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Sara a entendu : une étape après l'autre. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|C'est l'étape des œufs.
+narrateur|Les œufs sont chauds, tout doux.
+narrateur|Ils sont dans l'assiette ronde.
+narrateur|Une feuille est sur le doudou.
+maman|On fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Sarah goûte un petit bout.
+narrateur|Ça sent la ferme, le matin.
+enfant-f|C'est bon, maman.
+papa|Oui. Bravo, Sarah.
+papa|Tu as fait l'étape des œufs.
+maman|Ensuite, on met le doudou dans le sac.
+maman|Comme je t'ai dit.
+narrateur|Sarah met le doudou dans le sac.
+papa|Tu as mis ce que maman a dit.
+papa|Bravo.
+narrateur|Les œufs sont chauds dans l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15876,7 +16735,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'est levée. Elle s'est habillée. Elle est allée aux balançoires. Elle a pris le doudou. Puis c'était l'étape des œufs. Une étape après l'autre. Bravo, Sarah. Tu as fait du bon travail. J'ai fait les étapes. Les œufs sont chauds dans l'assiette. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16016,10 +16875,19 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr"/>
+          <t>narrateur|Sarah s'est levée.
+narrateur|Elle s'est habillée.
+narrateur|Elle est allée aux balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Puis c'était l'étape des œufs.
+maman|Une étape après l'autre.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai fait les étapes.
+narrateur|Les œufs sont chauds dans l'assiette.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16038,7 +16906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16132,6 +17000,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
